--- a/artfynd/A 14960-2026 artfynd.xlsx
+++ b/artfynd/A 14960-2026 artfynd.xlsx
@@ -4716,7 +4716,7 @@
         <v>133007537</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>133007514</v>
       </c>
       <c r="B34" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>133007525</v>
       </c>
       <c r="B35" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>133007543</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>133007487</v>
       </c>
       <c r="B46" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>133007474</v>
       </c>
       <c r="B52" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>133007539</v>
       </c>
       <c r="B59" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>133007484</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>133007490</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>133007505</v>
       </c>
       <c r="B64" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>133007509</v>
       </c>
       <c r="B73" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>133007549</v>
       </c>
       <c r="B74" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>133007499</v>
       </c>
       <c r="B82" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>133007512</v>
       </c>
       <c r="B94" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>133007472</v>
       </c>
       <c r="B104" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>133007517</v>
       </c>
       <c r="B110" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>133007529</v>
       </c>
       <c r="B111" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>133007531</v>
       </c>
       <c r="B112" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>133007527</v>
       </c>
       <c r="B116" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>133007494</v>
       </c>
       <c r="B125" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>133007479</v>
       </c>
       <c r="B132" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>133007502</v>
       </c>
       <c r="B133" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>133007469</v>
       </c>
       <c r="B134" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>133007521</v>
       </c>
       <c r="B138" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>133007546</v>
       </c>
       <c r="B154" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>

--- a/artfynd/A 14960-2026 artfynd.xlsx
+++ b/artfynd/A 14960-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY181"/>
+  <dimension ref="A1:AZ181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -812,6 +817,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007767</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -957,6 +967,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97264766</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1102,6 +1117,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97266577</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1233,6 +1253,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007595</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1364,6 +1389,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007598</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1495,6 +1525,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007600</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1635,6 +1670,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007602</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1761,6 +1801,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007603</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1887,6 +1932,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007605</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1999,6 +2049,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007709</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2116,6 +2171,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007711</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2233,6 +2293,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007712</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2350,6 +2415,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007714</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2462,6 +2532,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007715</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2574,6 +2649,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007718</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2691,6 +2771,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007719</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2808,6 +2893,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007721</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2915,6 +3005,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007724</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3022,6 +3117,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007725</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3129,6 +3229,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007727</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3236,6 +3341,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007729</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3343,6 +3453,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007730</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3450,6 +3565,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007732</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3562,6 +3682,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007733</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3674,6 +3799,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007735</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3814,6 +3944,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97267003</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3950,6 +4085,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007776</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4081,6 +4221,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007779</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4202,6 +4347,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007781</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4328,6 +4478,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007782</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4449,6 +4604,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007784</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4580,6 +4740,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007786</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4716,6 +4881,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007787</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4842,6 +5012,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007788</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4953,6 +5128,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007789</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5089,6 +5269,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007790</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5220,6 +5405,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007612</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5365,6 +5555,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235360</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5510,6 +5705,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235549</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5650,6 +5850,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235821</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5795,6 +6000,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97236255</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5940,6 +6150,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97264696</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6085,6 +6300,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97266527</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6230,6 +6450,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97266659</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6375,6 +6600,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97266769</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6515,6 +6745,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007628</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6655,6 +6890,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007630</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6786,6 +7026,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007632</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6922,6 +7167,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007633</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7067,6 +7317,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007635</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7203,6 +7458,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007636</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7339,6 +7599,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007638</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7474,6 +7739,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007639</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7609,6 +7879,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007641</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7749,6 +8024,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007644</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7884,6 +8164,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007647</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8024,6 +8309,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007648</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8160,6 +8450,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007650</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8290,6 +8585,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007652</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8421,6 +8721,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007653</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8547,6 +8852,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007656</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8683,6 +8993,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007658</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8823,6 +9138,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007659</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8954,6 +9274,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007661</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9085,6 +9410,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007664</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9220,6 +9550,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007665</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9355,6 +9690,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007667</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9495,6 +9835,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007668</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9635,6 +9980,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007670</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9775,6 +10125,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007672</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9915,6 +10270,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007674</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10055,6 +10415,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007675</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10181,6 +10546,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007678</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10321,6 +10691,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007679</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10457,6 +10832,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007682</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10597,6 +10977,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007684</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -10737,6 +11122,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007686</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10863,6 +11253,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007687</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10989,6 +11384,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007689</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11125,6 +11525,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007691</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11246,6 +11651,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007692</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11386,6 +11796,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007694</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11497,6 +11912,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007626</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11642,6 +12062,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235575</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -11787,6 +12212,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97236279</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11927,6 +12357,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007565</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12062,6 +12497,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007566</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12187,6 +12627,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007568</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12317,6 +12762,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007570</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -12452,6 +12902,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007572</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -12587,6 +13042,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007574</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -12722,6 +13182,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007577</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -12852,6 +13317,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007578</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12987,6 +13457,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007580</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13122,6 +13597,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007582</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -13252,6 +13732,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007583</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -13382,6 +13867,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007585</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -13507,6 +13997,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007587</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -13642,6 +14137,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007589</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -13777,6 +14277,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007591</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -13922,6 +14427,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235768</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -14062,6 +14572,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007792</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -14202,6 +14717,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97236175</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -14347,6 +14867,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97264865</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -14467,6 +14992,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007696</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -14602,6 +15132,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97266717</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -14737,6 +15272,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007469</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -14872,6 +15412,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007472</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -15007,6 +15552,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007474</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -15142,6 +15692,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007479</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -15277,6 +15832,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007484</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -15412,6 +15972,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007487</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -15547,6 +16112,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007490</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -15682,6 +16252,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007494</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -15817,6 +16392,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007499</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -15952,6 +16532,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007502</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -16087,6 +16672,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007505</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -16222,6 +16812,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007509</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -16357,6 +16952,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007512</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -16492,6 +17092,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007514</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -16627,6 +17232,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007517</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -16762,6 +17372,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007521</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -16897,6 +17512,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007525</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -17032,6 +17652,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007527</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -17167,6 +17792,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007529</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -17302,6 +17932,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007531</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -17437,6 +18072,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007537</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -17572,6 +18212,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007539</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -17707,6 +18352,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007543</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -17842,6 +18492,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007546</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -17977,6 +18632,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007549</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -18109,6 +18769,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007791</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -18227,6 +18892,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007813</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -18350,6 +19020,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007815</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -18468,6 +19143,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007816</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -18595,6 +19275,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007616</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -18722,6 +19407,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007618</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -18849,6 +19539,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007706</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -18981,6 +19676,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007707</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -19092,6 +19792,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007697</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -19208,6 +19913,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007699</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -19319,6 +20029,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007701</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -19430,6 +20145,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007702</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -19546,6 +20266,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007704</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -19679,6 +20404,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007738</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -19812,6 +20542,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007740</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -19945,6 +20680,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007742</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -20073,6 +20813,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007743</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -20201,6 +20946,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007745</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -20329,6 +21079,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007748</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -20462,6 +21217,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007750</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -20595,6 +21355,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007751</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -20728,6 +21493,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007753</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -20861,6 +21631,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007754</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -20989,6 +21764,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007757</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -21122,6 +21902,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007758</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -21250,6 +22035,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007759</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -21383,6 +22173,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007760</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -21516,6 +22311,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007762</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -21649,6 +22449,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007765</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -21765,6 +22570,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007464</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -21876,6 +22686,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007467</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -21988,6 +22803,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007624</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -22121,6 +22941,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007552</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -22237,6 +23062,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007794</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -22353,6 +23183,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007795</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -22469,6 +23304,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007796</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -22585,6 +23425,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007797</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -22696,6 +23541,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007798</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -22807,6 +23657,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007799</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -22918,6 +23773,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007800</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -23034,6 +23894,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007802</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -23145,6 +24010,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007803</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -23256,6 +24126,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007804</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -23372,6 +24247,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007807</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -23483,6 +24363,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007810</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -23594,6 +24479,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007811</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -23705,6 +24595,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007812</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -23834,6 +24729,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007559</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -23963,8 +24863,195 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133007561</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>